--- a/embeds/data/individual-family-community/slot-3-조혼인율과-조이혼율-및-합계출산율,-1970-2024.xlsx
+++ b/embeds/data/individual-family-community/slot-3-조혼인율과-조이혼율-및-합계출산율,-1970-2024.xlsx
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -545,7 +545,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -566,7 +566,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -650,7 +650,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -692,7 +692,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -776,7 +776,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -860,7 +860,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -881,7 +881,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -902,7 +902,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -923,7 +923,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -944,7 +944,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1007,7 +1007,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1028,7 +1028,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1049,7 +1049,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1070,7 +1070,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1112,7 +1112,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,7 +1133,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1154,7 +1154,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1196,7 +1196,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1217,7 +1217,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1238,7 +1238,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1301,7 +1301,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1322,7 +1322,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1406,7 +1406,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1448,7 +1448,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1532,7 +1532,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1574,7 +1574,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>합계출산율(명)</t>
+          <t>합계출산율</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1637,7 +1637,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1658,7 +1658,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1742,7 +1742,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1763,7 +1763,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1784,7 +1784,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1826,7 +1826,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1868,7 +1868,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1931,7 +1931,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1952,7 +1952,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1973,7 +1973,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1994,7 +1994,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2015,7 +2015,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2036,7 +2036,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2057,7 +2057,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2078,7 +2078,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2099,7 +2099,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2120,7 +2120,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2162,7 +2162,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2183,7 +2183,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2204,7 +2204,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2225,7 +2225,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2246,7 +2246,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2267,7 +2267,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2288,7 +2288,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2309,7 +2309,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2330,7 +2330,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2351,7 +2351,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2372,7 +2372,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2393,7 +2393,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2414,7 +2414,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2456,7 +2456,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2477,7 +2477,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2498,7 +2498,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2540,7 +2540,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2582,7 +2582,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2603,7 +2603,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2624,7 +2624,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2645,7 +2645,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2666,7 +2666,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2687,7 +2687,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2708,7 +2708,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2729,7 +2729,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2750,7 +2750,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>조혼인율(1,000명당 명)</t>
+          <t>조혼인율</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2771,7 +2771,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2813,7 +2813,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2834,7 +2834,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2855,7 +2855,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2876,7 +2876,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2897,7 +2897,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2918,7 +2918,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2939,7 +2939,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2960,7 +2960,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2981,7 +2981,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3044,7 +3044,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3065,7 +3065,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3086,7 +3086,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3107,7 +3107,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3128,7 +3128,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3149,7 +3149,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3191,7 +3191,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3212,7 +3212,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3233,7 +3233,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3254,7 +3254,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3275,7 +3275,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3296,7 +3296,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3317,7 +3317,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3338,7 +3338,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3359,7 +3359,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3380,7 +3380,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3401,7 +3401,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3464,7 +3464,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3485,7 +3485,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3506,7 +3506,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3527,7 +3527,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3548,7 +3548,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3569,7 +3569,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3590,7 +3590,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3611,7 +3611,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3632,7 +3632,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3653,7 +3653,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3674,7 +3674,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3695,7 +3695,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3716,7 +3716,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3737,7 +3737,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3758,7 +3758,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3821,7 +3821,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3842,7 +3842,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3863,7 +3863,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3884,7 +3884,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3905,7 +3905,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>조이혼율(1,000명당 명)</t>
+          <t>조이혼율</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
